--- a/lucas/import_data/utility/observation/excel/nominal_classes.xlsx
+++ b/lucas/import_data/utility/observation/excel/nominal_classes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
   <si>
     <t xml:space="preserve">indicator_id__indicator_name</t>
   </si>
@@ -37,135 +37,135 @@
     <t xml:space="preserve">abstract</t>
   </si>
   <si>
+    <t xml:space="preserve">soil texture usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 85–100% silt 0–15% clay 0–10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loamy sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loamy Sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 70–91% silt 0–30% clay 0–15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandy loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandy Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 43–80% silt 0–50% clay 0–20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 23–52% silt 28–50% clay 7–27%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silt Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 0–50% silt 50–100% clay 0–27%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 0–20% silt 80–100% clay 0–12%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandy clay loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandy Clay Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 45–80% silt 0–28% clay 20–35%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clay loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clay Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 20–45% silt 15–53% clay 27–40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silty clay loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silty Clay Loam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 0–20% silt 40–73% clay 27–40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandy clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandy Clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 45–65% silt 0–20% clay 35–55%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silty clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silty Clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 0–20% silt 40–60% clay 40–60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand 0–45% silt 0–40% clay 40–100%</t>
+  </si>
+  <si>
     <t xml:space="preserve">soil texture iuss</t>
   </si>
   <si>
-    <t xml:space="preserve">derived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 85–100% silt 0–15% clay 0–10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loamy sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loamy Sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 70–91% silt 0–30% clay 0–15%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandy loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandy Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 43–80% silt 0–50% clay 0–20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 23–52% silt 28–50% clay 7–27%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silty loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silty Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 0–50% silt 50–100% clay 0–27%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 0–20% silt 80–100% clay 0–12%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandy clay loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandy Clay Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 45–80% silt 0–28% clay 20–35%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clay loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clay Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 20–45% silt 15–53% clay 27–40%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silty clay loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silty Clay Loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 0–20% silt 40–73% clay 27–40%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandy clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandy Clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 45–65% silt 0–20% clay 35–55%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silty clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silty Clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 0–20% silt 40–60% clay 40–60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand 0–45% silt 0–40% clay 40–100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil texture usda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heavy clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy Clay</t>
-  </si>
-  <si>
     <t xml:space="preserve">sand 0–20% silt 0–45% clay 45–100%</t>
   </si>
   <si>
     <t xml:space="preserve">sand 0–20% silt 35–55% clay 45–65%</t>
   </si>
   <si>
+    <t xml:space="preserve">light clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Clay</t>
+  </si>
+  <si>
     <t xml:space="preserve">sand 20–55% silt 0–35% clay 45–65%</t>
   </si>
   <si>
@@ -178,12 +178,6 @@
     <t xml:space="preserve">sand 20–55% silt 15–55% clay 25–45%</t>
   </si>
   <si>
-    <t xml:space="preserve">silt loam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silt Loam</t>
-  </si>
-  <si>
     <t xml:space="preserve">sand 0–20% silt 55–100% clay 0–25%</t>
   </si>
   <si>
@@ -197,6 +191,36 @@
   </si>
   <si>
     <t xml:space="preserve">sand 90–100% silt 0–10% clay 0–10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy clayey soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Clayey Soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light clayey soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Clayey Soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loamy soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loamy Soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandy soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandy Soils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda major group</t>
   </si>
 </sst>
 </file>
@@ -493,13 +517,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="31.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -509,13 +534,13 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -526,13 +551,13 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -543,13 +568,13 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -560,13 +585,13 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -577,13 +602,13 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -594,13 +619,13 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -611,13 +636,13 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -628,13 +653,13 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -645,13 +670,13 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -662,13 +687,13 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -679,13 +704,13 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -696,13 +721,13 @@
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -713,13 +738,13 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -730,14 +755,14 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -747,14 +772,14 @@
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>47</v>
+      <c r="E15" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -764,13 +789,13 @@
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -781,13 +806,13 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -798,13 +823,13 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -815,13 +840,13 @@
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -832,13 +857,13 @@
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -849,14 +874,14 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -866,14 +891,14 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="0" t="s">
-        <v>55</v>
+      <c r="E22" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -883,14 +908,14 @@
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>56</v>
+      <c r="E23" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -900,14 +925,14 @@
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="0" t="s">
-        <v>57</v>
+      <c r="E24" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -917,24 +942,128 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D26" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1076,6 +1205,7 @@
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
